--- a/content/plan/raspisanie-12-25.10.xlsx
+++ b/content/plan/raspisanie-12-25.10.xlsx
@@ -706,32 +706,32 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:00 / 18:00</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Знакомство · конкурс</t>
+          <t>Знакомство · форматы</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Знакомьтесь: это зубр + конкурс имени (приз — билет)</t>
+          <t>Знакомьтесь: зубр + 9 форматов форума</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Карусель 4 сл. · CTA: имя в комментариях → билет</t>
+          <t>Рилс «Знакомьтесь, это зубр» (12:00) + карусель 5 сл. (18:00) · CTA: подпишитесь</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>Карусель 4 сл. + условия кратко · CTA: имя в комментариях</t>
+          <t>Клип с зубром + карусель · CTA: подпишитесь, ссылка на сайт</t>
         </is>
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>Пост с полными правилами конкурса (сроки, приз, условия)</t>
+          <t>Пост «9 форматов форума» полностью + рилс</t>
         </is>
       </c>
       <c r="I4" s="10" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
-          <t>Конкурс «Придумайте имя» + стикер «Вопрос» · отсчёт 32</t>
+          <t>Репост рилса + опрос «Какой формат интереснее?» · отсчёт 32</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="Q4" s="5" t="inlineStr">
         <is>
-          <t>content/nedeli-3-4_12.10-25.10/01-pn-12.10-znakomtes-zubr</t>
+          <t>content/nedeli-3-4_12.10-25.10/01-pn-12.10-zubr-formaty</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>Пост + отдельным сообщением чек-лист «12 причин» (закрепить на день)</t>
+          <t>Пост + PDF-чек-лист «12 причин» отдельным сообщением (закрепить на день)</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -878,42 +878,42 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00 + 19:00</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Мем</t>
+          <t>Розыгрыш + мем</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Родительский чат в 23:47</t>
+          <t>Розыгрыш билета (итоги 25.10) + мем «Родительский чат»</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Мем · CTA: отметьте коллегу</t>
+          <t>12:00 розыгрыш (2 сл.) · 19:00 мем · CTA: отметьте коллегу</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Мем · CTA: отметьте коллегу</t>
+          <t>Розыгрыш + мем · CTA: подписка и отметка коллеги</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>Мем (коротко)</t>
+          <t>Пост с полными условиями розыгрыша (закрепить) + мем</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>«Во сколько вам пришло последнее сообщение от родителя?»</t>
+          <t>«Во сколько вам пришло последнее сообщение от родителя?» + ссылка на розыгрыш</t>
         </is>
       </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>Мем + опрос «Отвечаете после 22:00?» · отсчёт 30</t>
+          <t>Сторис «Разыгрываем билет» + стикер-ссылка · отсчёт 30</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="Q6" s="5" t="inlineStr">
         <is>
-          <t>content/nedeli-3-4_12.10-25.10/03-sr-14.10-mem-roditelskiy-chat</t>
+          <t>content/nedeli-3-4_12.10-25.10/03-sr-14.10-rozygrysh-bileta</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>Последний день конкурса · обложка + ссылка · отсчёт 29</t>
+          <t>Обложка + «Сохраните» · отсчёт 29</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>Мем + нативный опрос «Имя для зубра» (5 вариантов)</t>
+          <t>Мем + рилс</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>Голосование за имя (стикер-опрос) · отсчёт 28</t>
+          <t>Мем + опрос «Какой форум выберете?» · напоминание о розыгрыше · отсчёт 28</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>Слайды «Утро» и «Вечер» + вопрос · голосование до 23:59 · отсчёт 27</t>
+          <t>Слайды «Утро» и «Вечер» + вопрос · отсчёт 27</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>11:00 / 12:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Итоги конкурса · вовлечение</t>
+          <t>Вовлечение</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>У зубра есть имя! + «Какой ты зубр сегодня?»</t>
+          <t>«Какой ты зубр сегодня?»</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>11:00 объявление победителя · 12:00 «Какой ты зубр»</t>
+          <t>«Какой ты зубр» + напоминание о розыгрыше</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>Поздравляем победителя + «Какой вы зубр сегодня?»</t>
+          <t>«Какой вы зубр сегодня?»</t>
         </is>
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>Сторис-победитель (имя + ник) · отсчёт 26</t>
+          <t>Картинка + опрос · отсчёт 26</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -1829,37 +1829,37 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Вовлечение · итоги</t>
+          <t>Итоги розыгрыша</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Объясните, что вы владелец спортшколы, не говоря об этом</t>
+          <t>Итоги розыгрыша билета</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>Картинка · CTA: ответ в комментариях</t>
+          <t>Картинка-победитель · CTA: стартовая цена для первых 50</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>Картинка · CTA: ответ в комментариях</t>
+          <t>Картинка · CTA: забронировать (#tickets)</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>Пост-вопрос + итоги двух недель</t>
+          <t>Пост-итоги + видео выбора победителя</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>Итоги двух недель: лучшие ответы, что дальше</t>
+          <t>Поздравляем победителя + итоги двух недель</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>Картинка + стикер «Вопрос» · отсчёт 19</t>
+          <t>Сторис-победитель + отметка · отсчёт 19</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>content/nedeli-3-4_12.10-25.10/14-vs-25.10-objasni</t>
+          <t>content/nedeli-3-4_12.10-25.10/14-vs-25.10-itogi-rozygrysha</t>
         </is>
       </c>
     </row>

--- a/content/plan/raspisanie-12-25.10.xlsx
+++ b/content/plan/raspisanie-12-25.10.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Рилс «Знакомьтесь, это зубр» (12:00) + карусель 5 сл. (18:00) · CTA: подпишитесь</t>
+          <t>Рилс «Знакомьтесь, это зубр» (12:00, версия без звука + трендовый трек, удар на 2-й секунде) + карусель 5 сл. (18:00) · CTA: подпишитесь</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Сколько стоит потерянный клиент</t>
+          <t>Сколько стоит потерянный клиент + чек-лист «12 причин» (PDF)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>5 фраз, которые удерживают после пробного</t>
+          <t>5 фраз, которые удерживают клиента после пробного занятия</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1055,12 +1055,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Мем + рилс · голосование</t>
+          <t>Мем + рилс</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>«Нет / Да» про форумы + рилс «Полный зал»</t>
+          <t>«Нет / Да» про форумы (верх — ч/б зубр) + рилс «Полный зал»</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
